--- a/PM1MKT.xlsx
+++ b/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t/>
   </si>
   <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA SRL 189 ML</t>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -28,151 +28,151 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRG 5X91 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MI STO 5x76 G</t>
-  </si>
-  <si>
-    <t>20113383</t>
-  </si>
-  <si>
-    <t>ROMA KLP FRS 6x23 G</t>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20113989</t>
-  </si>
-  <si>
-    <t>ROMA KLP C CKL 186 G</t>
-  </si>
-  <si>
-    <t>20088730</t>
-  </si>
-  <si>
-    <t>KNZLR SNGL KEJU 60 G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20141057</t>
-  </si>
-  <si>
-    <t>KNZLR S TOM YUM 60 G</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600 ML</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPCINO 10X25 G</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>K/A SPC MIX 10x23 G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHESY 102 G</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORI 102 G</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT D 160 ML</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20038763</t>
-  </si>
-  <si>
-    <t>PNTENE SHP AD 160 ML</t>
-  </si>
-  <si>
-    <t>10003569</t>
-  </si>
-  <si>
-    <t>CLOSE UP GRN F 160 G</t>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MIN 600 ML</t>
+  </si>
+  <si>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 685G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113403</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH O&amp;C 100</t>
+  </si>
+  <si>
+    <t>20130710</t>
+  </si>
+  <si>
+    <t>LUX BW SKURA BLM 825</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>20046056</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLUS 150</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20027095</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20131625</t>
+  </si>
+  <si>
+    <t>LARISST FCL.TIS 250S</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FH 100 G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C.LANG KYU PTH 60 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG BAYI LVD 60 G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLGHT LME PCH 660 G</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SNLGHT J/NIPIS 675 G</t>
   </si>
 </sst>
 </file>
@@ -565,14 +565,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,15 +632,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -652,15 +652,15 @@
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -669,38 +669,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -709,38 +709,38 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -757,10 +757,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -772,15 +772,15 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -789,18 +789,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -809,190 +809,170 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/PM1MKT.xlsx
+++ b/PM1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMND 52 G</t>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/DAY MOCCA 10x20 G</t>
   </si>
   <si>
     <t>PM1MKT</t>
@@ -31,121 +31,139 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHW 52 G</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PG 65 G</t>
+    <t>20143384</t>
+  </si>
+  <si>
+    <t>K/A B.CFE S 10X2.2 G</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535 G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535 G</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG SPC 80 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR S.JB 129 G</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINE 1.5 L</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MIN 600 ML</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK TH MLTI 350 ML</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TH MLTI 1.3 L</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CO BISC 104 G</t>
+  </si>
+  <si>
+    <t>20143290</t>
+  </si>
+  <si>
+    <t>NISSIN WFR C.LV 50 G</t>
+  </si>
+  <si>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABE CHIP SWD 65 G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20114757</t>
+  </si>
+  <si>
+    <t>GURIBEE R.LAUT 65 G</t>
+  </si>
+  <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LT SP NR 65 G</t>
-  </si>
-  <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POPCRN CRML 75 G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20108264</t>
-  </si>
-  <si>
-    <t>SARI ROTI TAWAR JMBO</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210 ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STW TP 225 ML</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG CKT TP 225 ML</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600 ML</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500 ML</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PSODENT WHT 225 G</t>
+    <t>10003569</t>
+  </si>
+  <si>
+    <t>CLOSE UP GRN F 160 G</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FH 100 G</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20118537</t>
-  </si>
-  <si>
-    <t>PSODENT WHT 120+30 G</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LI LVDR 510 ML</t>
-  </si>
-  <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SOKLN DT FL 700 ML</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SH G.BL 160 ML</t>
-  </si>
-  <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MNT 160 ML</t>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SNLGHT JRK NPS 400 G</t>
   </si>
   <si>
     <t>10005482</t>
@@ -154,13 +172,10 @@
     <t>SNLGHT LME PCH 660 G</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SNLGHT J/NIPIS 675 G</t>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
   </si>
 </sst>
 </file>
@@ -553,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -680,44 +695,44 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -737,38 +752,38 @@
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -777,7 +792,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -785,10 +800,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -797,7 +812,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -805,22 +820,22 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,13 +849,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,113 +869,133 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
